--- a/pcmeltco_50yr.xlsx
+++ b/pcmeltco_50yr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ariannenantel/Documents/USRA/USRA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0DCD98BF-BEB4-7144-A65D-E28B4CC0576F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D83980-8C08-F84D-9486-7F5615B115FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32160" yWindow="1580" windowWidth="27640" windowHeight="16680" xr2:uid="{23212528-6FBB-4E4C-A70A-BAC09A720782}"/>
+    <workbookView xWindow="-19200" yWindow="600" windowWidth="19200" windowHeight="21000" xr2:uid="{23212528-6FBB-4E4C-A70A-BAC09A720782}"/>
   </bookViews>
   <sheets>
     <sheet name="pcmeltco_50yr" sheetId="1" r:id="rId1"/>
